--- a/erp-server/erp-server-oms/src/main/resources/excel/kolB2bApplicationError.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/kolB2bApplicationError.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <r>
       <rPr>
@@ -246,6 +246,9 @@
   </si>
   <si>
     <t>项目名称</t>
+  </si>
+  <si>
+    <t>明细备注</t>
   </si>
   <si>
     <t>错误数据</t>
@@ -1329,66 +1332,66 @@
         <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
